--- a/JsonConverter/ExcelFiles/UnitTable.xlsx
+++ b/JsonConverter/ExcelFiles/UnitTable.xlsx
@@ -33,85 +33,85 @@
     <x:t>화면 표시 이름</x:t>
   </x:si>
   <x:si>
+    <x:t>AttackDamage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackInterval</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DetectionRange</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Addressables 프리팹 키</x:t>
+  </x:si>
+  <x:si>
+    <x:t>근접 전투 로봇</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AttackRange</x:t>
+  </x:si>
+  <x:si>
     <x:t>PrefabKey</x:t>
   </x:si>
   <x:si>
+    <x:t>UnitType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유닛 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DisplayName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxHealth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoveSpeed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브레이브 로봇</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enemy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 HP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유닛 유형</x:t>
+  </x:si>
+  <x:si>
     <x:t>이동 속도</x:t>
   </x:si>
   <x:si>
+    <x:t>stirng</x:t>
+  </x:si>
+  <x:si>
     <x:t>적 탐색 범위</x:t>
   </x:si>
   <x:si>
     <x:t>Unit/Enemy/MeleeRobot</x:t>
   </x:si>
   <x:si>
-    <x:t>Hero</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DisplayName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 HP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>stirng</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유닛 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxHealth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UnitType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackDamage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브레이브 로봇</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
     <x:t>Unit/Hero/BraveRobot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유닛 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoveSpeed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hero_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>근접 전투 로봇</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackInterval</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DetectionRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AttackRange</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Addressables 프리팹 키</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Enemy</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -929,25 +929,25 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G1" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H1" s="3" t="s">
         <x:v>1</x:v>
@@ -956,18 +956,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>19</x:v>
@@ -988,50 +988,50 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="J2" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="14" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F3" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I3" s="13" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J3" s="13" t="s">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D4" s="5">
         <x:v>100</x:v>
@@ -1052,7 +1052,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
@@ -1065,16 +1065,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="5">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E5" s="5">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="5">
         <x:v>2</x:v>
@@ -1089,7 +1089,7 @@
         <x:v>1.2</x:v>
       </x:c>
       <x:c r="J5" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K5" s="5"/>
       <x:c r="L5" s="5"/>
@@ -2339,7 +2339,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>